--- a/markets/prospects/Saudi_Arabia_Fashion_Prospects.xlsx
+++ b/markets/prospects/Saudi_Arabia_Fashion_Prospects.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Master Prospects'!$A$1:$J$163</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision Makers'!$A$1:$G$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1311,9 +1311,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/bedoon-essm</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Osamah Habis</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>City Director, Riyadh</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Saqib Saeed</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Manager Retail Brand Marketing - KSA (incl. Under Armour), GMG (Jan 2024-present)</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>VP, Chief Digital Officer - Omnichannel Digital Innovation, Al Tayer Insignia (group-level, Dubai; covers KSA)</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp +971545821753</t>
+          <t>WhatsApp +971545821753, +9668002450025</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Darine Sabbagh</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager E-commerce &amp; Omnichannel, Chalhoub Group (May 2024-present)</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Yohei Takahashi</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, ASICS SA Marketing LLC (Riyadh) (Jul 2024-present)</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Darine Sabbagh</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager E-commerce &amp; Omnichannel, Chalhoub Group (May 2024-present)</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Patrick McMahon</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ecommerce Lead, Tory Burch, Chalhoub Group (Jun 2024-present; Dubai-based, regional)</t>
         </is>
       </c>
     </row>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Adam Sharma</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Online Trading &amp; Digital Marketing, Foot Locker / New Balance MENA (Alshaya Group; Dubai-based)</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohamad Awamleh</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital / E-Commerce Manager, Al-Futtaim (KSA online retail for monobrands incl. Marks &amp; Spencer) (Sep 2024-present)</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hany Mokhtar</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ecommerce Manager</t>
         </is>
       </c>
     </row>
@@ -2567,9 +2567,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/imtiaz</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chahd Madi</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Country Retail Manager - Prada Saudi Arabia (Riyadh), Apr 2023-present</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2724,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Michelle Hirst</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of Ecommerce, South-East Hub (SE Europe, Middle East, Africa, CIS) - Calvin Klein &amp; Tommy Hilfiger, PVH (Dubai)</t>
         </is>
       </c>
     </row>
@@ -2815,19 +2815,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/shein</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammad Dwaikat</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Country General Manager, SHEIN Middle East</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rema Fiaz</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>E-commerce Product Lead, Al Othaim Life</t>
         </is>
       </c>
     </row>
@@ -3062,12 +3062,12 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Aden Nuh</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital Marketing Manager - Fashion, Chalhoub Group</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Arman Hossain</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>E-commerce Manager</t>
         </is>
       </c>
     </row>
@@ -3301,19 +3301,19 @@
           <t>info@family.sa</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/family-mall</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammad Kamal</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Marketing Officer (CMO)</t>
         </is>
       </c>
     </row>
@@ -3349,19 +3349,19 @@
           <t>reachus@femi9.com</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fad-international</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Hala Beyari</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager (Femi9 &amp; Vivid Flair), Fad International</t>
         </is>
       </c>
     </row>
@@ -3397,9 +3397,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>https://sa.linkedin.com/company/darlena-fashion</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3445,19 +3445,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/barllina/</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Abdullah Al-Eissawi</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Executive Officer, Barllina</t>
         </is>
       </c>
     </row>
@@ -3596,12 +3596,12 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Virginie Mamodbay</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sports Brands Director, Cenomi Retail (Decathlon KSA franchise operator; former Decathlon KSA brand &amp; e-commerce launch lead)</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3644,12 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ammar Tahan</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>CEO and Co-owner, Armada Retail Concept (RIVA owner), Kuwait - Jan 2001-present</t>
         </is>
       </c>
     </row>
@@ -3685,19 +3685,19 @@
           <t>eseven.store@gmail.com</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eseven-store</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Areej Mohsen</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Social Media Manager / E-Store Management</t>
         </is>
       </c>
     </row>
@@ -3836,12 +3836,12 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Jonathan Bannister</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing GCC, PUMA Group (Feb 2025-present; Dubai-based)</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dexter Fernandes</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>E-commerce Manager, Alyasra Fashion (Kuwait) - Oct 2023-present</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>info@alammari.sa</t>
+          <t>info@alammari.sa, waleed@alammaritex.com</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Salem Al-Ammari</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager (Salem Hassan Al-Ammari Sons Co.)</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Maya Saab</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Digital &amp; Partnerships, Rubaiyat Group (KSA distributor)</t>
         </is>
       </c>
     </row>
@@ -4416,12 +4416,12 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>VP, Chief Digital Officer - Omnichannel Digital Innovation, Al Tayer Insignia (group-level, Dubai; covers KSA)</t>
         </is>
       </c>
     </row>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Zahiya Hassan Tawil</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Marketing and Communications, Valentino (Dubai/Middle East) - Jan 2025-present</t>
         </is>
       </c>
     </row>
@@ -4505,19 +4505,19 @@
           <t>sales@opera-sa.com</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/operafashionsa</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Basel Almaflehi</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Al-Hattami</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -5083,19 +5083,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/ipekyol-group</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ertugrul Yildiz</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital Marketing Manager, Ipekyol Group</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Dan Monaghan</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager, A&amp;F-Hollister (Majid Al Futtaim)</t>
         </is>
       </c>
     </row>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Tarek Barakat</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing &amp; E-commerce Director, Beside Group (KSA distributor)</t>
         </is>
       </c>
     </row>
@@ -5471,19 +5471,19 @@
           <t>team@swag.com.sa</t>
         </is>
       </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/swag-trading-company</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Qasim AlKhazraji</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Rema Fiaz</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>E-commerce Product Lead, Al Othaim Life</t>
         </is>
       </c>
     </row>
@@ -5615,19 +5615,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/semir-international</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shu Chen-Haberman</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of E-commerce and Marketing, International Division, Semir Group</t>
         </is>
       </c>
     </row>
@@ -5711,9 +5711,9 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/louzanabaya</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mazin Almoallim</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>President/CEO, Almoallim United</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>VP, Chief Digital Officer - Omnichannel Digital Innovation, Al Tayer Insignia (group-level, Dubai; covers KSA)</t>
         </is>
       </c>
     </row>
@@ -5999,19 +5999,19 @@
           <t>lavallee.zd@gmail.com</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/najd-international-trading%C2%A0co</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Aminah Ba Qutaybah</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Social Media Account Manager &amp; Content Creator</t>
         </is>
       </c>
     </row>
@@ -6095,19 +6095,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/semir-international</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Shu Chen-Haberman</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of E-commerce and Marketing, International Division, Semir Group</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Nijood Mohammed Rashed Alharigy (نجود محمد راشد الحريقي)</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder / Owner, Dar Nijood (دار نجود) online store and app, Jeddah</t>
         </is>
       </c>
     </row>
@@ -6239,19 +6239,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H119" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/springfield-clothing</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Carmen Argüello Olivares</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>International Marketing Manager (franchise), Springfield</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Waleed Malik</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager, Al Moallim United (Kate Spade KSA)</t>
         </is>
       </c>
     </row>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Sarah Eldridge</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Director of Strategic Partnerships &amp; E-Commerce</t>
         </is>
       </c>
     </row>
@@ -6584,12 +6584,12 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Mohammed Al Shakaa</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Operating Officer (since Jan 2024) &amp; Director of Sales and Business Development, Kafak International Company - leads Jasmine Lingerie KSA retail</t>
         </is>
       </c>
     </row>
@@ -6632,12 +6632,12 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Michele Lorusso</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Marketing &amp; Communication Officer</t>
         </is>
       </c>
     </row>
@@ -6675,19 +6675,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/yoox-net-a-porter</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Celine Lefebvre</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>General Manager - Fashion, Beauty, Jewelry, Watches, Lifestyle (MENA), YOOX NET-A-PORTER (Middle East JV; serves yoox.com/sa)</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Assem El Sawadi</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder, Advesto (advsto) Adventure Store</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Abdullah Ali</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
     </row>
@@ -6819,9 +6819,9 @@
           <t>reeman.design@gmail.com</t>
         </is>
       </c>
-      <c r="H131" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/reeman-design</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Alaaeddin Haroun</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Brand Director - Abercrombie &amp; Fitch, Majid Al Futtaim Ventures (P&amp;L KSA/Oman/Bahrain/Qatar), Jan 2018-present</t>
         </is>
       </c>
     </row>
@@ -7013,9 +7013,9 @@
           <t>elegntpalace@gmail.com</t>
         </is>
       </c>
-      <c r="H135" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/elegantpalace</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ibtihal Alkhateeb</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Brand &amp; Product Manager</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="G139" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>mtjrlezaz@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -7250,22 +7250,22 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Not found</t>
+          <t>info@azadea.com</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/calzedonia</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Marta Kratzer</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Ecommerce, Calzedonia Group</t>
         </is>
       </c>
     </row>
@@ -7308,12 +7308,12 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Adam Sharma</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Head of Online Trading &amp; Digital Marketing, Foot Locker / New Balance MENA (Alshaya Group; Dubai-based)</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>+966556668717, WhatsApp +966556668717</t>
+          <t>+966556668717, WhatsApp +966556668717, +966138333111</t>
         </is>
       </c>
       <c r="G143" s="6" t="inlineStr">
@@ -7397,19 +7397,19 @@
           <t>info@ndfashions.com</t>
         </is>
       </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H143" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/company/ndfashions</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Ahmed Alabdulkareem</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder &amp; CEO, ND Fashion Group (also CEO Akarem Group), Al Khobar</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Matjary_k@hotmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Khawla Bokhari</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Founder / Owner</t>
         </is>
       </c>
     </row>
@@ -7500,12 +7500,12 @@
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Katrine Boel Olesen</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>E-commerce Operational Manager, JACK &amp; JONES and JJXX (BESTSELLER, jackjones.com webshop)</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>+966555346360, WhatsApp +966555346360</t>
+          <t>+966555346360, WhatsApp +966555346360, +966552731911</t>
         </is>
       </c>
       <c r="G147" s="6" t="inlineStr">
         <is>
-          <t>myille.ksa@gmail.com</t>
+          <t>myille.ksa@gmail.com, myille.co@gmail.com</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
@@ -7685,19 +7685,19 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="H149" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aivi-world</t>
         </is>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Vivek Rajukumar</t>
         </is>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Chief Executive Officer, AIVI (Apparel Group)</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>+966556699396, WhatsApp +966556699396</t>
+          <t>+966556699396, WhatsApp +966556699396, +966126736187</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="G155" s="6" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@stylish.com.sa</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Aden Nuh</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>Digital Marketing Manager - Fashion, Chalhoub Group</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>+966580276738, WhatsApp +966580276738</t>
+          <t>+966580276738, WhatsApp +966580276738, +966557301317</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -8405,193 +8405,215 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId236"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8604,7 +8626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10210,22 +10232,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Gucci Saudi Arabia</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>https://shop.mango.com/sa/</t>
+          <t>https://www.gucci.com/sa/</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Aida Moudden</t>
+          <t>Osamah Habis</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Country Manager - Africa, Middle East &amp; Franchises, MANGO</t>
+          <t>City Director, Riyadh</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10240,29 +10262,29 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/aidamoudden</t>
+          <t>https://linkedin.com/in/osamah-habis-06024aba</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Gucci Saudi Arabia</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>https://shop.mango.com/sa/</t>
+          <t>https://www.gucci.com/sa/</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Claire Shields</t>
+          <t>Marcello Boffa</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>International Country &amp; Merchandising Manager (Middle East incl. e-commerce/DTC plans), MANGO</t>
+          <t>EMEA Head of Digital Business</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -10277,29 +10299,29 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/claire-shields-802378151</t>
+          <t>https://linkedin.com/in/marcello-boffa-b6659749</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>American Eagle</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.com.sa/</t>
+          <t>https://shop.mango.com/sa/</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Rob Silsbury</t>
+          <t>Aida Moudden</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Vice President Marketing &amp; eCommerce, Alshaya Group (American Eagle franchise operator)</t>
+          <t>Country Manager - Africa, Middle East &amp; Franchises, MANGO</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10314,29 +10336,29 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/robsilsbury</t>
+          <t>https://www.linkedin.com/in/aidamoudden</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>American Eagle</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>https://www.americaneagle.com.sa/</t>
+          <t>https://shop.mango.com/sa/</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Kory Mumin</t>
+          <t>Claire Shields</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Head of Ecommerce Operations, Alshaya Group</t>
+          <t>International Country &amp; Merchandising Manager (Middle East incl. e-commerce/DTC plans), MANGO</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -10351,29 +10373,29 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/kory-mumin</t>
+          <t>https://www.linkedin.com/in/claire-shields-802378151</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Styli</t>
+          <t>أندر آرمر السعودية</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>https://stylishop.com/sa/en/</t>
+          <t>https://www.underarmour.sa/ar/</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Shibu Tharakan</t>
+          <t>Saqib Saeed</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CEO, Styli (Landmark Group)</t>
+          <t>Manager RBM - KSA (Nike, Under Armour, etc.), GMG</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10388,29 +10410,29 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/shibutharakan</t>
+          <t>https://linkedin.com/in/saqibsaeedq</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Lefties</t>
+          <t>متجر بلومينغديلز اونلاين | أشهر والمزيد</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>https://www.lefties.com/sa/</t>
+          <t>https://mamasandpapas.com.sa/</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Ali Badran</t>
+          <t>Sumit Srivastava</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+          <t>VP, Chief Digital Officer - Omnichannel Digital Innovation, Al Tayer Insignia (Jan 2024-present)</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -10425,29 +10447,29 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+          <t>https://www.linkedin.com/in/sumitsrivastavaglobal</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Lefties</t>
+          <t>Guess KSA</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>https://www.lefties.com/sa/</t>
+          <t>https://www.guess.sa/</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Adel Alamin</t>
+          <t>Darine Sabbagh</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+          <t>General Manager E-commerce &amp; Omnichannel, Chalhoub Group (Dubai)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10462,29 +10484,29 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+          <t>https://linkedin.com/in/sdarine</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>Bershka</t>
+          <t>Guess KSA</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/sa/</t>
+          <t>https://www.guess.sa/</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Ali Badran</t>
+          <t>Muhammad Hamza Muzaffar</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+          <t>Head of eCommerce, Digital &amp; CRM, Chalhoub Group (Dubai)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -10499,29 +10521,29 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+          <t>https://linkedin.com/in/hamzamuzaffar1995</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Bershka</t>
+          <t>Asics</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/sa/</t>
+          <t>https://www.asics.com/sa/</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Adel Alamin</t>
+          <t>Yohei Takahashi</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+          <t>General Manager, ASICS SA Marketing LLC (Riyadh)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10536,29 +10558,29 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+          <t>https://www.linkedin.com/in/yohei-takahashi-94404017</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>richy</t>
+          <t>Asics</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>https://richy.sa/</t>
+          <t>https://www.asics.com/sa/</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Mohammed Alajlan</t>
+          <t>Megha Sinha</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>CEO at Richy</t>
+          <t>Senior Manager Ecommerce, ASICS Arabia (Dubai; regional incl. KSA)</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -10573,29 +10595,29 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohammed-alajlan-6aa2245a</t>
+          <t>https://www.linkedin.com/in/megha-sinha-1698035</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Massimo Dutti</t>
+          <t>American Eagle</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/sa/</t>
+          <t>https://www.americaneagle.com.sa/</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Ali Badran</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+          <t>Vice President Marketing &amp; eCommerce, Alshaya Group (American Eagle franchise operator)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -10610,29 +10632,29 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>Massimo Dutti</t>
+          <t>American Eagle</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/sa/</t>
+          <t>https://www.americaneagle.com.sa/</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Adel Alamin</t>
+          <t>Kory Mumin</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+          <t>Head of Ecommerce Operations, Alshaya Group</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -10647,29 +10669,29 @@
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+          <t>https://www.linkedin.com/in/kory-mumin</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Stradivarius</t>
+          <t>Lacoste</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/sa/</t>
+          <t>https://www.lacoste.sa/</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Ali Badran</t>
+          <t>Darine Sabbagh</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+          <t>General Manager E-commerce &amp; Omnichannel, Chalhoub Group (Dubai)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10684,29 +10706,29 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+          <t>https://linkedin.com/in/sdarine</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>Stradivarius</t>
+          <t>Lacoste</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/sa/</t>
+          <t>https://www.lacoste.sa/</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Adel Alamin</t>
+          <t>Joelle Assadourian</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+          <t>Regional Marketing Manager, Fashion Franchise, Chalhoub Group (Dubai)</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -10721,29 +10743,29 @@
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+          <t>https://linkedin.com/in/joelle-assadourian-8088166a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear</t>
+          <t>Tory Burch</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/sa/</t>
+          <t>https://www.toryburch.sa/</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Ali Badran</t>
+          <t>Patrick McMahon</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+          <t>Ecommerce Lead - Tory Burch, Chalhoub Group</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10758,29 +10780,29 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+          <t>https://www.linkedin.com/in/patrickmcmahon5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear</t>
+          <t>Styli</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/sa/</t>
+          <t>https://stylishop.com/sa/en/</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Adel Alamin</t>
+          <t>Shibu Tharakan</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+          <t>CEO, Styli (Landmark Group)</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -10795,29 +10817,29 @@
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+          <t>https://www.linkedin.com/in/shibutharakan</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>العقيلات للوازم المقناص والرحلات</t>
+          <t>New Balance Saudi Arabia</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>https://aloqiylat.com/</t>
+          <t>https://www.newbalance.com.sa/en/</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>mohammed Aljuraysh</t>
+          <t>Adam Sharma</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>ALOQIYLAT company founder Aljuraysh</t>
+          <t>Head of Online Trading &amp; Digital Marketing, Foot Locker / New Balance MENA (Alshaya Group; Dubai-based, covers KSA)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -10832,29 +10854,29 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohammed-aljuraysh-037862b0</t>
+          <t>https://www.linkedin.com/in/gagansharma9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Giordano Online</t>
+          <t>New Balance Saudi Arabia</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>https://giordano.com.sa/ar</t>
+          <t>https://www.newbalance.com.sa/en/</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Ahmadullah Abdul Hadi</t>
+          <t>Anjali Bohara</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Managing Director at Giordano KSA</t>
+          <t>Senior Marketing Manager, Alshaya Group (omni-channel marketing and e-commerce P&amp;L for Foot Locker, New Balance etc., MENA)</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -10869,29 +10891,29 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ahmadullahabdulhadi</t>
+          <t>https://www.linkedin.com/in/anjali-bohara-21b96a64</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>كيابي السعودية</t>
+          <t>New Balance Saudi Arabia</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>https://kiabi.sa/ar</t>
+          <t>https://www.newbalance.com.sa/en/</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Orlane Renard</t>
+          <t>Rob Silsbury</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Head of Marketing at Kiabi AMEA</t>
+          <t>Vice President Marketing &amp; Ecommerce, Alshaya Group (MENA, Dubai-based)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -10906,29 +10928,29 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/orlane-renard-301541120</t>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Luxury: Saint Laurent</t>
+          <t>ماركس آند سبنسر السعودية</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>https://www.ysl.com/en-sa/</t>
+          <t>https://www.marksandspencer.sa/ar/fashion</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Fredrik Blomqvist</t>
+          <t>Mohamad Awamleh</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Luxury Brand Hotel General Manager</t>
+          <t>Digital / E-Commerce Manager, Al-Futtaim (KSA, monobrand online retail)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -10943,29 +10965,29 @@
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fredrik-blomqvist</t>
+          <t>https://linkedin.com/in/mohamad-awamleh-6862b825a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Oysho</t>
+          <t>Samena</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/sa/</t>
+          <t>https://samena-stores.com/</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Ali Badran</t>
+          <t>Hany Mokhtar</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+          <t>Ecommerce Manager (head of department), Samena</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -10980,29 +11002,29 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+          <t>https://linkedin.com/in/hany-mokhtar1441</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>Oysho</t>
+          <t>Lefties</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/sa/</t>
+          <t>https://www.lefties.com/sa/</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Adel Alamin</t>
+          <t>Ali Badran</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -11017,29 +11039,29 @@
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Lefties</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>https://www.splashfashions.com/sa/</t>
+          <t>https://www.lefties.com/sa/</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Ipsa Kalra</t>
+          <t>Adel Alamin</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>AVP &amp; Head of E-commerce - Splash Fashions</t>
+          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -11054,29 +11076,29 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ipsa-kalra-a364b88b</t>
+          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Maje KSA</t>
+          <t>Bershka</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>https://maje.sa/</t>
+          <t>https://www.bershka.com/sa/</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Mohamad Awamleh</t>
+          <t>Ali Badran</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Digital / E-Commerce Manager, Al-Futtaim (KSA monobrands)</t>
+          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -11091,29 +11113,29 @@
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohamad-awamleh-6862b825a</t>
+          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Maje KSA</t>
+          <t>Bershka</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>https://maje.sa/</t>
+          <t>https://www.bershka.com/sa/</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Mohamed Farid</t>
+          <t>Adel Alamin</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Head of Operations &amp; Business Development, Al-Futtaim Retail KSA</t>
+          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -11128,29 +11150,29 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohamedfarid2</t>
+          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>Maje KSA</t>
+          <t>Prada</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>https://maje.sa/</t>
+          <t>https://www.prada.com/sa/ar.html</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>Pamela Sapitan</t>
+          <t>Chahd Madi</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Ecommerce Operations Team Lead (Sandro, Maje, Ted Baker - UAE/KSA/Qatar/Kuwait), Al-Futtaim</t>
+          <t>Country Retail Manager, Prada Group - Saudi Arabia (Riyadh)</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -11165,29 +11187,29 @@
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pamelasapitan</t>
+          <t>https://linkedin.com/in/chahd-madi-mba-5b6b1375</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Reebok Saudi</t>
+          <t>Calvin Klein</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>https://www.reebok.sa/</t>
+          <t>https://www.calvinklein.sa/</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Vishal VijayKumar</t>
+          <t>Michelle Hirst</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Head of Omnichannel (ex-Head of Ecommerce &amp; Marketing), Al Boom Marine - Reebok UAE/KSA operator</t>
+          <t>Director of Ecommerce, South-East Hub (incl. Middle East) - Calvin Klein &amp; Tommy Hilfiger, PVH</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -11202,29 +11224,29 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/vishalvkumar</t>
+          <t>https://www.linkedin.com/in/michelle-hirst</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>Reebok Saudi</t>
+          <t>richy</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>https://www.reebok.sa/</t>
+          <t>https://richy.sa/</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Ahmed Abdelmaaboud</t>
+          <t>Mohammed Alajlan</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>E-commerce Operations Executive (Reebok UAE &amp; KSA), Al Boom Marine</t>
+          <t>CEO at Richy</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -11239,29 +11261,29 @@
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/ahmed-abdelmaaboud-a23a3892</t>
+          <t>https://www.linkedin.com/in/mohammed-alajlan-6aa2245a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>HUGO BOSS</t>
+          <t>SHEIN Middle East</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>https://www.hugoboss.com/sa/</t>
+          <t>https://ar.shein.com/</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Mohamad Awamleh</t>
+          <t>Mohammad Dwaikat</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Digital / E-Commerce Manager, Al-Futtaim (KSA monobrands)</t>
+          <t>Country General Manager, SHEIN Middle East</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -11274,31 +11296,31 @@
           <t>Not found</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/mohamad-awamleh-6862b825a</t>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>HUGO BOSS</t>
+          <t>SHEIN GCC</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>https://www.hugoboss.com/sa/</t>
+          <t>https://ar.shein.com/</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>Mohamed Farid</t>
+          <t>Lin Wang (王麟)</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Head of Operations &amp; Business Development, Al-Futtaim Retail KSA</t>
+          <t>Senior Marketing Manager, GCC Region</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -11313,29 +11335,29 @@
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mohamedfarid2</t>
+          <t>https://linkedin.com/in/%E9%BA%9F-%E7%8E%8B-1ab532152</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>HUGO BOSS</t>
+          <t>La Vie En Rose Saudi Arabia (Al Othaim Life)</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>https://www.hugoboss.com/sa/</t>
+          <t>https://www.lavieenrose.com.sa/</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Pamela Sapitan</t>
+          <t>Rema Fiaz</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Operations Team Lead (Sandro, Maje, Ted Baker - UAE/KSA/Qatar/Kuwait), Al-Futtaim</t>
+          <t>E-commerce Product Lead (La Vie en Rose &amp; Ziddy), Al Othaim Life</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -11345,34 +11367,34 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Not found</t>
+          <t>info@lavieenrose.com.sa</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/pamelasapitan</t>
+          <t>https://linkedin.com/in/rema-fiaz-7a9863223</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>kaafmeem</t>
+          <t>Michael Kors Saudi Arabia</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>https://kaafmeem.com/en</t>
+          <t>https://www.michaelkors.sa/</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Mayyar Saleh</t>
+          <t>Aden Nuh</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; CEO at KaafMeem</t>
+          <t>Head of Digital Marketing / Digital Marketing Manager - Fashion, Chalhoub Group (Michael Kors, Max Mara etc. across UAE, KSA, Kuwait; Dubai)</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -11387,29 +11409,29 @@
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mayyar-saleh-699b6917</t>
+          <t>https://linkedin.com/in/aden-nuh-50835214</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>kaafmeem</t>
+          <t>Massimo Dutti</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>https://kaafmeem.com/en</t>
+          <t>https://www.massimodutti.com/sa/</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Karima Saleh</t>
+          <t>Ali Badran</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Co- Founder / CCO, KaafMeem</t>
+          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11424,29 +11446,29 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/karimasaleh</t>
+          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>Columbia Saudi Arabia</t>
+          <t>Massimo Dutti</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>https://columbia.sa/</t>
+          <t>https://www.massimodutti.com/sa/</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Lana Alfehaid</t>
+          <t>Adel Alamin</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Co -President, Saudi Students Association at Columbia University</t>
+          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -11461,29 +11483,29 @@
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/lanaalfehaid</t>
+          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DeFacto</t>
+          <t>SEASON LifeStyle</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>https://www.defacto.com/en-sa/</t>
+          <t>https://season.sa/</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Hany AlKholy</t>
+          <t>Arman Hossain</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Country Manager - Defacto, DeFacto</t>
+          <t>E-commerce Manager</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -11498,49 +11520,3046 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hany-alkholy-15646430</t>
+          <t>https://linkedin.com/in/arman-hossain-099aa7291</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
+          <t>SEASON LifeStyle</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>https://season.sa/</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Malek Arafa</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/malek-arafa-a61a71205</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SEASON LifeStyle</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>https://season.sa/</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Musa Al-Mutairi</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Chairman of the Board</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Stradivarius</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.stradivarius.com/sa/</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Ali Badran</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Stradivarius</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stradivarius.com/sa/</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Adel Alamin</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Pull&amp;Bear</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pullandbear.com/sa/</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Ali Badran</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Pull&amp;Bear</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pullandbear.com/sa/</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Adel Alamin</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Family Mall (مجمع العائلة)</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>https://family.sa/</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Mohammad Kamal</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Chief Marketing Officer (CMO)</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Family Mall (مجمع العائلة)</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>https://family.sa/</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Sattam Al-Mathani</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sattam-al-mathani-213181166</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Femi9 (Fad International)</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.femi9.com/</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Hala Beyari</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Manager (leads Femi9 &amp; Vivid Flair)</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/hala-beyari-6b3a5228</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Femi9 (Fad International)</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.femi9.com/</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Eyad Abdullah Mashat</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO, Fad International</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>بارلينا</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>https://barllina.com/ar-us/</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Abdullah Al-Eissawi (عبدالله العيسائي)</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer (الرئيس التنفيذي), Barllina</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>العقيلات للوازم المقناص والرحلات</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>https://aloqiylat.com/</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>mohammed Aljuraysh</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>ALOQIYLAT company founder Aljuraysh</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohammed-aljuraysh-037862b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>ديكاتلون السعودية</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>https://decathlon.com.sa/</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Virginie Mamodbay</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Sports Brands Director, Cenomi Retail (runs sports brands BU incl. retail network and e-commerce mono-brand websites; Riyadh)</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/virginie-mamodbay</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>ديكاتلون السعودية</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>https://decathlon.com.sa/</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Redouane Bali</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Head of Digital Africa &amp; Middle East, Decathlon (Feb 2024-present)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/redouane-bali</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Riva Fashion: Shop Women's Clothes and Accessories Online</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.rivafashion.com/ar-sa/</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Ammar Tahan</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>CEO and Co-owner, Armada Retail Concept (RIVA/Choice owner)</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>https://kw.linkedin.com/in/ammar-tahan-56306524</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Riva Fashion: Shop Women's Clothes and Accessories Online</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rivafashion.com/ar-sa/</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Muhannad Abu Taleb</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Senior E-Commerce, Armada Retail Concept (Kuwait)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/muhannad-abu-taleb-494aa5125</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Riva Fashion: Shop Women's Clothes and Accessories Online</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.rivafashion.com/ar-sa/</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Haifa Zawahreh</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Head of Digital Growth, Armada Retail Concept</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>E-SEVEN STORE</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>https://eseven-store.com/en</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Areej Mohsen</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Social Media Manager / E-Store Management (Salla, Amazon, Noon)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/areej-mohsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Giordano Online</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>https://giordano.com.sa/ar</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Ahmadullah Abdul Hadi</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Managing Director at Giordano KSA</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ahmadullahabdulhadi</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>PUMA</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>https://sa.puma.com/sa/ar</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Jonathan Bannister</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing GCC, PUMA Group (regional, Dubai; incl. Saudi campaigns)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonathan-bannister-72287a48</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>PUMA</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>https://sa.puma.com/sa/ar</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Sylvia Hanein</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Senior Manager E-Commerce Content &amp; CRM GCC, PUMA Group (Dubai)</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sylvia-hanein-61622314</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>PUMA</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>https://sa.puma.com/sa/ar</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Johan Kuhlo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director GCC, PUMA (oversees UAE, Saudi Arabia, Qatar, Kuwait, Oman; from Sep 2024)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>DKNY | Saudi Arabia Official Store</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>https://dkny.sa/</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Dexter Fernandes</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Manager, Alyasra Fashion (Kuwait) - GCC fashion e-commerce incl. DKNY</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dexter-fernandes-2783ab113</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>DKNY | Saudi Arabia Official Store</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>https://dkny.sa/</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Magui Daher</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Regional Brand Manager - DKNY &amp; Donna Karan New York, Alyasra Fashion (Kuwait)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>https://kw.linkedin.com/in/magui-daher-5b95a584</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>كيابي السعودية</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>https://kiabi.sa/ar</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Orlane Renard</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Head of Marketing at Kiabi AMEA</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/orlane-renard-301541120</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Luxury: Saint Laurent</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ysl.com/en-sa/</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Fredrik Blomqvist</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Luxury Brand Hotel General Manager</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fredrik-blomqvist</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Oysho</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.oysho.com/sa/</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Ali Badran</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Director - Zara &amp; Inditex (Cenomi Retail, KSA)</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ali-badran-b8603065</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Oysho</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.oysho.com/sa/</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Adel Alamin</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director Inditex (Zara Home, Massimo Dutti, Bershka, Stradivarius, Oysho, Pull&amp;Bear, Lefties), Cenomi</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adel-alamin-76284b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Al Ammari Fabrics (Salem Hassan Al-Ammari Sons Co.)</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>https://alammari.sa/</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Waleed Salem Al-Ammari</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Director of Fabrics Department</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>waleed@alammaritex.com</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Al Ammari Fabrics (Salem Hassan Al-Ammari Sons Co.)</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>https://alammari.sa/</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Salem Al-Ammari</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>General Manager (Salem Hassan Al-Ammari Sons Co.)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Splash</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>https://www.splashfashions.com/sa/</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Ipsa Kalra</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>AVP &amp; Head of E-commerce - Splash Fashions</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ipsa-kalra-a364b88b</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Balenciaga (Rubaiyat Group, KSA distributor)</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.balenciaga.com/en-sa/</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Maya Saab</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Head of Digital &amp; Partnerships, Rubaiyat Group</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mayasaab-es</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>جيمشارك السعودية</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>https://www.gymshark.sa/</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Sumit Srivastava</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>VP, Chief Digital Officer - Omnichannel Digital Innovation, Al Tayer Insignia (Jan 2024-present)</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sumitsrivastavaglobal</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Valentino Online Boutique: The Maison Valentino Official Site</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.valentino.com/en-sa/</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Zahiya Hassan Tawil</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing and Communications, Valentino (Middle East, Dubai)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/zahiya-hassan-tawil-a7428423</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>Opera Fashion</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>https://opera-fashion.com/</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Basel Almaflehi</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/basel-almaflehi-075518175</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Sharqiaa (Bait Abaya Sharqiaa Co.)</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>https://store.sharqiaa.com/en</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Al-Hattami</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohammed-al-hattami-5a1baa207</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>Sharqiaa (Bait Abaya Sharqiaa Co.)</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>https://store.sharqiaa.com/en</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Ramzi Al-Hattami</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ramzialhattami</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Maje KSA</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>https://maje.sa/</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Mohamad Awamleh</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Digital / E-Commerce Manager, Al-Futtaim (KSA monobrands)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamad-awamleh-6862b825a</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>Maje KSA</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>https://maje.sa/</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Mohamed Farid</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Head of Operations &amp; Business Development, Al-Futtaim Retail KSA</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamedfarid2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Maje KSA</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>https://maje.sa/</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Pamela Sapitan</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Operations Team Lead (Sandro, Maje, Ted Baker - UAE/KSA/Qatar/Kuwait), Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pamelasapitan</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Reebok Saudi</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>https://www.reebok.sa/</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Vishal VijayKumar</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Head of Omnichannel (ex-Head of Ecommerce &amp; Marketing), Al Boom Marine - Reebok UAE/KSA operator</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vishalvkumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Reebok Saudi</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reebok.sa/</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Abdelmaaboud</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Operations Executive (Reebok UAE &amp; KSA), Al Boom Marine</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ahmed-abdelmaaboud-a23a3892</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>Ipekyol Group (KSA)</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>https://sa.ipekyol.com/</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Ertugrul Yildiz</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager, Ipekyol Group</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ertugrulyildiz-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>HUGO BOSS</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hugoboss.com/sa/</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Mohamad Awamleh</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Digital / E-Commerce Manager, Al-Futtaim (KSA monobrands)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamad-awamleh-6862b825a</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>HUGO BOSS</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hugoboss.com/sa/</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>Mohamed Farid</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Head of Operations &amp; Business Development, Al-Futtaim Retail KSA</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohamedfarid2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>HUGO BOSS</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hugoboss.com/sa/</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Pamela Sapitan</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Operations Team Lead (Sandro, Maje, Ted Baker - UAE/KSA/Qatar/Kuwait), Al-Futtaim</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pamelasapitan</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Hollister KSA (Majid Al Futtaim for Fashion SPC)</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hollisterco.sa/</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Dan Monaghan</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>General Manager, Abercrombie &amp; Fitch - Hollister (Majid Al Futtaim)</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/dan-monaghan-4923b013</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Hollister KSA (Majid Al Futtaim for Fashion SPC)</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hollisterco.sa/</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Ghada Makarem</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Marketing and Communications Manager, MAF Fashion</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ghada-makarem-8b3b2743</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Fred Perry</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fredperry.com/sa-en/</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>Tarek Barakat</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Marketing &amp; E-commerce Director, Beside Group</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/tarek-barakat-23b83132</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Swag Trading Company</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>https://swag.sa/en</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Qasim AlKhazraji</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Manager (مدير التسويق)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/qasimalkhazraji</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Ziddy KSA (Al Othaim Life)</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>https://ziddy.sa/</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Rema Fiaz</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>E-commerce Product Lead (La Vie en Rose &amp; Ziddy), Al Othaim Life</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/rema-fiaz-7a9863223</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Semir Group (Semir KSA)</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>https://semir.com.sa/</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Shu Chen-Haberman</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Director of E-commerce and Marketing, International Division, Semir Group</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Rosa Clara Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>https://rosaclara.sa/</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Mazin Almoallim</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>President/CEO, Almoallim United</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mazin-almoallim</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>kaafmeem</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>https://kaafmeem.com/en</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Mayyar Saleh</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; CEO at KaafMeem</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mayyar-saleh-699b6917</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>kaafmeem</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>https://kaafmeem.com/en</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Karima Saleh</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Co- Founder / CCO, KaafMeem</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/karimasaleh</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Columbia Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>https://columbia.sa/</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Lana Alfehaid</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Co -President, Saudi Students Association at Columbia University</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lanaalfehaid</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>https://www.gap.sa/</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Sumit Srivastava</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>VP, Chief Digital Officer - Omnichannel Digital Innovation, Al Tayer Insignia (Jan 2024-present)</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sumitsrivastavaglobal</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>LAVALLEE (Najd International Trading Co)</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>https://lavalleeshop.com/</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Aminah Ba Qutaybah</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Social Media Account Manager &amp; Content Creator (marketing)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/aminah-ba-qutaybah-0533b8112</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>Balabala KSA (Semir Group)</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>https://balabala.com.sa/</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Shu Chen-Haberman</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>Director of E-commerce and Marketing, International Division, Semir Group</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Dar nijood</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>https://darnijood.com/</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Nijood Mohammed Rashed Alharigy (نجود محمد راشد الحريقي)</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Founder / Owner, Dar Nijood (دار نجود) online store and app, Jeddah</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>+966592490004</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>darnijood@gmail.com</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/nijood-alharigy-79b99b35b</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>Springfield KSA (Tendam)</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>https://www.springfield.sa/</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Carmen Argüello Olivares</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>International Marketing Manager (franchise markets), Springfield</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/carmen-arguello</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Kate Spade Saudi Arabia (Al Moallim United)</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.katespade.sa/</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Waleed Malik</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager (Coach, Kate Spade, Cole Haan &amp; others), Al Moallim United</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/waleed-malik-63b988ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>River Island (Saudi Arabia)</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>https://www.riverisland.com/sa/</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Sarah Eldridge</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Director of Strategic Partnerships &amp; E-Commerce</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sarah-eldridge-312a1b64</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>DeFacto</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.defacto.com/en-sa/</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Hany AlKholy</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Country Manager - Defacto, DeFacto</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hany-alkholy-15646430</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>Jasmine Store Luxury Women Pajamas and Lingerie</t>
+        </is>
+      </c>
+      <c r="B143" s="7" t="inlineStr">
+        <is>
+          <t>https://jasmine.com.sa/en</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Mohammed Al Shakaa</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer (since Jan 2024) &amp; Director of Sales and Business Development, Kafak International Company - leads Jasmine Lingerie KSA retail</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/mohammed-al-shakaa-aa9735b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>ETRO (Saudi Arabia)</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>https://www.etro.com/sa-en/</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Michele Lorusso</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Chief Marketing &amp; Communication Officer</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/michele-lorusso-8603a210</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>YOOX</t>
+        </is>
+      </c>
+      <c r="B145" s="7" t="inlineStr">
+        <is>
+          <t>https://www.yoox.com/sa/</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Celine Lefebvre</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>General Manager - Fashion, Beauty, Jewelry, Watches, Lifestyle (MENA), YOOX NET-A-PORTER (Middle East JV; serves yoox.com/sa)</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/celine-lefebvre-b0a3a65</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>advsto | متجر المغامرين</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>https://advsto.sa/</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Assem El Sawadi</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Founder, Advesto (advsto) Adventure Store</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>KNO A Dress (Kanwa Women's Clothing Est.)</t>
+        </is>
+      </c>
+      <c r="B147" s="7" t="inlineStr">
+        <is>
+          <t>https://knoadress.com/en</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Abdullah Ali</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/abdullah-ali-93bb7931b</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>https://www.abercrombie.sa/</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Alaaeddin Haroun</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Brand Director - Abercrombie &amp; Fitch, Majid Al Futtaim Lifestyle (Dubai)</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/alaaeddin-haroun-301715116</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>https://www.abercrombie.sa/</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Fahed Ghanim</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>CEO, Majid Al Futtaim Lifestyle</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
           <t>Noētic</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>https://noetic.sa/</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Renad Nagro</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>General manager @Noeticsa</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/in/renad-nagro-b3408a208</t>
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>Selene Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>https://selene-official.com/en</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>Ibtihal Alkhateeb</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>Brand &amp; Product Manager</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ibtihal-alkhateeb-a690611b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Calzedonia Saudi Arabia (Azadea franchise)</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>https://www.calzedonia.com/sa/</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Marta Kratzer</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Head of Ecommerce, Calzedonia Group</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>info@azadea.com</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/marta-kratzer</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>Foot Locker</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/sa/</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Adam Sharma</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>Head of Online Trading &amp; Digital Marketing, Foot Locker / New Balance MENA (Alshaya Group; Dubai-based, covers KSA)</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gagansharma9</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Foot Locker</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/sa/</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Anjali Bohara</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Senior Marketing Manager, Alshaya Group (omni-channel marketing and e-commerce P&amp;L for Foot Locker, New Balance etc., MENA)</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anjali-bohara-21b96a64</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>Foot Locker</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/sa/</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Rob Silsbury</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>Vice President Marketing &amp; Ecommerce, Alshaya Group (MENA, Dubai-based)</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robsilsbury</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>ND Fashion فساتين سهرة وزفاف فاخرة في الخبر</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>https://ndfashions.com/</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Alabdulkareem</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; CEO, ND Fashion Group (also CEO Akarem Group), Al Khobar</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ahmed-alabdulkareem</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>خولة لفن الحياكة</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>https://yarn-art-khawla.com/</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>Khawla Bokhari (خولة بخاري)</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>Founder / Owner (signs store About page as crochet &amp; yarn artist; Telegram: "Khawla Yarn Art Foundation")</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>+966533089374</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>Matjary_k@hotmail.com</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>JACK &amp; JONES</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>https://www.jackjones.com/ar-sa</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Katrine Boel Olesen</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce Operational Manager, JACK &amp; JONES and JJXX (BESTSELLER, jackjones.com webshop)</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/katrine-boel-olesen-45760522</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>aivi</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>https://en-sa.aivi.com/</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>Vivek Rajukumar</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, AIVI (Apparel Group)</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/vivek-rajukumar</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Max Mara KSA</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>https://www.maxmara.sa/</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Aden Nuh</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Head of Digital Marketing / Digital Marketing Manager - Fashion, Chalhoub Group (Michael Kors, Max Mara etc. across UAE, KSA, Kuwait; Dubai)</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/aden-nuh-50835214</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G79"/>
+  <autoFilter ref="A1:G160"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -11669,21 +14688,169 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B128" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B129" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B130" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B131" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B132" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B133" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B134" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B135" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B136" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G150" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G151" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G152" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G153" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G154" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G155" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G156" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G158" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G159" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G160" r:id="rId290"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
